--- a/artfynd/A 3604-2025 artfynd.xlsx
+++ b/artfynd/A 3604-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122890340</v>
+        <v>122890341</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543830</v>
+        <v>543819</v>
       </c>
       <c r="R2" t="n">
-        <v>6990504</v>
+        <v>6990517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890341</v>
+        <v>122890340</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543819</v>
+        <v>543830</v>
       </c>
       <c r="R3" t="n">
-        <v>6990517</v>
+        <v>6990504</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 3604-2025 artfynd.xlsx
+++ b/artfynd/A 3604-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122890341</v>
+        <v>122890340</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543819</v>
+        <v>543830</v>
       </c>
       <c r="R2" t="n">
-        <v>6990517</v>
+        <v>6990504</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890340</v>
+        <v>122890341</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543830</v>
+        <v>543819</v>
       </c>
       <c r="R3" t="n">
-        <v>6990504</v>
+        <v>6990517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 3604-2025 artfynd.xlsx
+++ b/artfynd/A 3604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122890340</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>122890341</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
